--- a/output/pdf_financials_xlsx/GRL.xlsx
+++ b/output/pdf_financials_xlsx/GRL.xlsx
@@ -1919,10 +1919,10 @@
         <v>0</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>1.050415</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>1.476813</v>
       </c>
     </row>
     <row r="93">
@@ -3163,7 +3163,11 @@
           <t>Share-based payment reserve 7</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/GRL.xlsx
+++ b/output/pdf_financials_xlsx/GRL.xlsx
@@ -615,7 +615,7 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.00735</v>
       </c>
     </row>
     <row r="13">
@@ -867,7 +867,7 @@
         <v>-3.409761</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-4.987129</v>
+        <v>-4.994479</v>
       </c>
     </row>
     <row r="28">
@@ -899,7 +899,7 @@
         <v>-3.3957</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-4.980461</v>
+        <v>-4.987811</v>
       </c>
     </row>
     <row r="30">
@@ -976,13 +976,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.016135</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.397373</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>10.54889</v>
       </c>
     </row>
     <row r="35">
@@ -1008,13 +1008,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.016135</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.397373</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>10.54889</v>
       </c>
     </row>
     <row r="37">
@@ -1200,13 +1200,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.066357</v>
+        <v>0.050222</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.848265</v>
+        <v>0.450892</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>10.891453</v>
+        <v>0.342563</v>
       </c>
     </row>
     <row r="49">
@@ -2685,7 +2685,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -5715,7 +5715,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">

--- a/output/pdf_financials_xlsx/GRL.xlsx
+++ b/output/pdf_financials_xlsx/GRL.xlsx
@@ -2198,7 +2198,7 @@
         <v>0</v>
       </c>
       <c r="C110" s="3" t="n">
-        <v>0</v>
+        <v>0.007951</v>
       </c>
       <c r="D110" s="3" t="n">
         <v>0</v>
@@ -3619,7 +3619,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E34" t="inlineStr">
         <is>
           <t>-</t>
